--- a/input/timetable/Техносферная безопасность.xlsx
+++ b/input/timetable/Техносферная безопасность.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28650" windowHeight="13890" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28650" windowHeight="13890"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -332,9 +332,6 @@
     <t>Основы первой доврачебной помощи, п/г 2, А401</t>
   </si>
   <si>
-    <t>Электроника и электротехника, п/г 1, А104//</t>
-  </si>
-  <si>
     <t>Экологический мониторинг (пр), А401//  Экологический мониторинг, п/г 2, А401</t>
   </si>
   <si>
@@ -408,9 +405,6 @@
     <t>Иностранный язык в профессиональной сфере (пр), А503</t>
   </si>
   <si>
-    <t>Государственный пожарный надзор (лек)/(пр), А320</t>
-  </si>
-  <si>
     <t>Спец.оценка условий труда и произв. контроль, п/г 1, А402//</t>
   </si>
   <si>
@@ -448,6 +442,12 @@
   </si>
   <si>
     <t>Безопасность технологических процессов и производств (пр), А401</t>
+  </si>
+  <si>
+    <t>Государственный пожарный надзор (лек)/(пр), А509</t>
+  </si>
+  <si>
+    <t>Электроника и электротехника, п/г 1, А401//</t>
   </si>
 </sst>
 </file>
@@ -3080,7 +3080,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="133" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D16" s="134"/>
       <c r="E16" s="134"/>
@@ -3094,11 +3094,11 @@
         <v>1</v>
       </c>
       <c r="C17" s="146" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D17" s="147"/>
       <c r="E17" s="147" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F17" s="148"/>
       <c r="M17" s="62"/>
@@ -3109,7 +3109,7 @@
         <v>2</v>
       </c>
       <c r="C18" s="136" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D18" s="137"/>
       <c r="E18" s="137"/>
@@ -3509,7 +3509,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="121" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D11" s="122"/>
       <c r="E11" s="122"/>
@@ -3521,7 +3521,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="79" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D12" s="80"/>
       <c r="E12" s="80"/>
@@ -3533,7 +3533,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="207" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D13" s="208"/>
       <c r="E13" s="208"/>
@@ -3545,7 +3545,7 @@
         <v>4</v>
       </c>
       <c r="C14" s="172" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D14" s="173"/>
       <c r="E14" s="173"/>
@@ -3571,7 +3571,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="79" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D16" s="80"/>
       <c r="E16" s="80"/>
@@ -3583,7 +3583,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="196" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D17" s="197"/>
       <c r="E17" s="197"/>
@@ -3605,7 +3605,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="146" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D19" s="147"/>
       <c r="E19" s="147"/>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D20" s="125"/>
       <c r="E20" s="203" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F20" s="132"/>
     </row>
@@ -3631,7 +3631,7 @@
         <v>3</v>
       </c>
       <c r="C21" s="124" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D21" s="125"/>
       <c r="E21" s="203" t="s">
@@ -3645,7 +3645,7 @@
         <v>4</v>
       </c>
       <c r="C22" s="118" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D22" s="119"/>
       <c r="E22" s="119"/>
@@ -3659,11 +3659,11 @@
         <v>1</v>
       </c>
       <c r="C23" s="164" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="D23" s="165"/>
       <c r="E23" s="165" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F23" s="214"/>
     </row>
@@ -3685,7 +3685,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="196" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D25" s="197"/>
       <c r="E25" s="197"/>
@@ -3733,7 +3733,7 @@
         <v>5</v>
       </c>
       <c r="C29" s="79" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D29" s="80"/>
       <c r="E29" s="80"/>
@@ -3747,7 +3747,7 @@
       <c r="C30" s="183"/>
       <c r="D30" s="184"/>
       <c r="E30" s="185" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F30" s="186"/>
     </row>
@@ -3759,7 +3759,7 @@
         <v>2</v>
       </c>
       <c r="C31" s="121" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D31" s="122"/>
       <c r="E31" s="122"/>
@@ -3771,7 +3771,7 @@
         <v>3</v>
       </c>
       <c r="C32" s="118" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D32" s="119"/>
       <c r="E32" s="119"/>
@@ -4159,7 +4159,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="97" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D12" s="98"/>
       <c r="E12" s="98"/>
@@ -4179,7 +4179,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="175" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D13" s="176"/>
       <c r="E13" s="176"/>
@@ -4229,7 +4229,7 @@
         <v>2</v>
       </c>
       <c r="I15" s="178" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J15" s="179"/>
       <c r="K15" s="179"/>
@@ -4249,7 +4249,7 @@
         <v>3</v>
       </c>
       <c r="I16" s="124" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J16" s="131"/>
       <c r="K16" s="131"/>
@@ -4261,7 +4261,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="79" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D17" s="80"/>
       <c r="E17" s="74"/>
@@ -4271,7 +4271,7 @@
         <v>4</v>
       </c>
       <c r="I17" s="124" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="J17" s="131"/>
       <c r="K17" s="131"/>
@@ -4285,7 +4285,7 @@
       <c r="C18" s="118"/>
       <c r="D18" s="221"/>
       <c r="E18" s="222" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F18" s="120"/>
       <c r="G18" s="33"/>
@@ -4327,7 +4327,7 @@
         <v>3</v>
       </c>
       <c r="C20" s="124" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D20" s="131"/>
       <c r="E20" s="131"/>
@@ -4347,7 +4347,7 @@
         <v>4</v>
       </c>
       <c r="C21" s="124" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D21" s="131"/>
       <c r="E21" s="131"/>
@@ -4407,7 +4407,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="124" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D24" s="131"/>
       <c r="E24" s="131"/>
@@ -4417,7 +4417,7 @@
         <v>3</v>
       </c>
       <c r="I24" s="79" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J24" s="80"/>
       <c r="K24" s="80"/>
@@ -4439,7 +4439,7 @@
         <v>4</v>
       </c>
       <c r="I25" s="124" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J25" s="131"/>
       <c r="K25" s="131"/>
@@ -4521,7 +4521,7 @@
         <v>7</v>
       </c>
       <c r="I29" s="124" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J29" s="131"/>
       <c r="K29" s="131"/>
@@ -4543,7 +4543,7 @@
         <v>8</v>
       </c>
       <c r="I30" s="249" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J30" s="185"/>
       <c r="K30" s="185"/>
@@ -4569,7 +4569,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="164" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J31" s="165"/>
       <c r="K31" s="165"/>
@@ -4591,7 +4591,7 @@
         <v>2</v>
       </c>
       <c r="I32" s="79" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J32" s="80"/>
       <c r="K32" s="80"/>
@@ -4603,11 +4603,11 @@
         <v>3</v>
       </c>
       <c r="C33" s="79" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D33" s="80"/>
       <c r="E33" s="80" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F33" s="81"/>
       <c r="G33" s="47"/>
@@ -4615,7 +4615,7 @@
         <v>3</v>
       </c>
       <c r="I33" s="124" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J33" s="131"/>
       <c r="K33" s="131"/>

--- a/input/timetable/Техносферная безопасность.xlsx
+++ b/input/timetable/Техносферная безопасность.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28650" windowHeight="13890"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28650" windowHeight="13890" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="181">
   <si>
     <t>пара</t>
   </si>
@@ -71,6 +71,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -131,6 +134,21 @@
     <t>ТО</t>
   </si>
   <si>
+    <t>Бушева Ж.И.</t>
+  </si>
+  <si>
+    <t>Кузнецова А.А.</t>
+  </si>
+  <si>
+    <t>Ончева Е.М.</t>
+  </si>
+  <si>
+    <t>Шапошникова И.В.</t>
+  </si>
+  <si>
+    <t>Насирова А.Р.</t>
+  </si>
+  <si>
     <t>Безопасность жизнедеятельности (лек 32 ч)</t>
   </si>
   <si>
@@ -152,6 +170,27 @@
     <t>Правоведение  (лек 32 ч)</t>
   </si>
   <si>
+    <t>Владимирова Г.Е.</t>
+  </si>
+  <si>
+    <t>Горшкова О.О.</t>
+  </si>
+  <si>
+    <t>Кузнецова Ю.В.</t>
+  </si>
+  <si>
+    <t>Фомина Е.Р.</t>
+  </si>
+  <si>
+    <t>Андреева Т.С.</t>
+  </si>
+  <si>
+    <t>Жогаль А.В.</t>
+  </si>
+  <si>
+    <t>Ходунькова Н.А.</t>
+  </si>
+  <si>
     <t>305-31</t>
   </si>
   <si>
@@ -164,6 +203,9 @@
     <t>Экология техносферы (пр), А403</t>
   </si>
   <si>
+    <t>Лепихин С.А.</t>
+  </si>
+  <si>
     <t>Экологический мониторинг, п/г 1, А401//</t>
   </si>
   <si>
@@ -179,6 +221,12 @@
     <t>История России (лек 32 ч)</t>
   </si>
   <si>
+    <t>Мягких К.П.</t>
+  </si>
+  <si>
+    <t>Белощенко Д.В.</t>
+  </si>
+  <si>
     <t>Медико-биологические основы безопасности человека (пр), А403</t>
   </si>
   <si>
@@ -188,6 +236,9 @@
     <t>Высшая математика (пр), А615</t>
   </si>
   <si>
+    <t>Ибрагимова Н.И.</t>
+  </si>
+  <si>
     <t>Законодательство в области охраны труда, пожарной и промышленной безопасности (лек), А401</t>
   </si>
   <si>
@@ -215,6 +266,9 @@
     <t>Электроника и электротехника (лек), А401</t>
   </si>
   <si>
+    <t>Сало В.Э.</t>
+  </si>
+  <si>
     <t>Экологический мониторинг (лек), А401</t>
   </si>
   <si>
@@ -224,6 +278,9 @@
     <t>Системы защиты среды обитания (пр), А401</t>
   </si>
   <si>
+    <t>Барков Д.Н.</t>
+  </si>
+  <si>
     <t>Специальные требования промышленной безопасности в строительной отрасли (лек), А403</t>
   </si>
   <si>
@@ -269,9 +326,24 @@
     <t>02-02.2026-04.04.2025</t>
   </si>
   <si>
+    <t>Сташкин П.Р.</t>
+  </si>
+  <si>
+    <t>Шадрин Г.А.</t>
+  </si>
+  <si>
     <t>Высшая математика (лек), А615//</t>
   </si>
   <si>
+    <t>Калинина Е.А.</t>
+  </si>
+  <si>
+    <t>Сердюков Д.В.</t>
+  </si>
+  <si>
+    <t>Кузнецова С.В.</t>
+  </si>
+  <si>
     <t>Основы российской государственности (пр), А410</t>
   </si>
   <si>
@@ -287,9 +359,18 @@
     <t>Основы предпринимательской деятельности (лек 16 ч)</t>
   </si>
   <si>
+    <t>Смирнова И.В.</t>
+  </si>
+  <si>
     <t>Менеджмент в техносферной безопасности (пр), А403// Основы работы с данными (лек), А403</t>
   </si>
   <si>
+    <t>Ончева Е.М./Мягких К.П.</t>
+  </si>
+  <si>
+    <t>Лепихин С.А./Кузнецова Ю.В.</t>
+  </si>
+  <si>
     <t>Разработка и реализация проектов по вопросам безопасности (лек)/(пр), А401</t>
   </si>
   <si>
@@ -323,6 +404,9 @@
     <t>Основы предпринимательской деятельности (пр), К711//</t>
   </si>
   <si>
+    <t>Галюта О.Н.</t>
+  </si>
+  <si>
     <t>Основы экономической культуры (лек 32 ч)</t>
   </si>
   <si>
@@ -330,6 +414,12 @@
   </si>
   <si>
     <t>Основы первой доврачебной помощи, п/г 2, А401</t>
+  </si>
+  <si>
+    <t>Лысенкова А.В.</t>
+  </si>
+  <si>
+    <t>Ибрагимова Н.И. ; Лысенкова А.В.</t>
   </si>
   <si>
     <t>Экологический мониторинг (пр), А401//  Экологический мониторинг, п/г 2, А401</t>
@@ -381,6 +471,18 @@
     <t>Методологические основы бакалаврской работы (лек)/(пр), А521</t>
   </si>
   <si>
+    <t>Курц М.А.</t>
+  </si>
+  <si>
+    <t>Карама Е.А.</t>
+  </si>
+  <si>
+    <t>Яременко Д.А.</t>
+  </si>
+  <si>
+    <t>Иванов С.А.</t>
+  </si>
+  <si>
     <t>Проектирование систем обеспечения пожарной безопасности (пр), А521</t>
   </si>
   <si>
@@ -420,18 +522,27 @@
     <t>Противопожарное водоснабжение (лек), А403</t>
   </si>
   <si>
+    <t>Жогаль А.В./Иванов С.А.</t>
+  </si>
+  <si>
     <t>Противопожарное водоснабжение (лек), А402*// Прогнозирование опасных факторов пожара (лек), А401</t>
   </si>
   <si>
     <t>Противопожарное водоснабжение (пр), А402*// Прогнозирование опасных факторов пожара (пр), А401</t>
   </si>
   <si>
+    <t xml:space="preserve">Лысенкова А.В.;Ибрагимова Н.И. </t>
+  </si>
+  <si>
     <t>Специальные требования промышленной безопасности в нефтегазовой отрасли (лек), А410</t>
   </si>
   <si>
     <t>//Специальные требования промышленной безопасности в нефтегазовой отрасли (пр), А401</t>
   </si>
   <si>
+    <t>Шукурова И.В.; Мягких К.П.</t>
+  </si>
+  <si>
     <t>Безопасность технологических процессов и производств (лек), А401</t>
   </si>
   <si>
@@ -442,6 +553,15 @@
   </si>
   <si>
     <t>Безопасность технологических процессов и производств (пр), А401</t>
+  </si>
+  <si>
+    <t>Джумаева А.А.</t>
+  </si>
+  <si>
+    <t>Петров Е.А.; Гурова Л.Д.</t>
+  </si>
+  <si>
+    <t>Петров Е.А.</t>
   </si>
   <si>
     <t>Государственный пожарный надзор (лек)/(пр), А509</t>
@@ -571,7 +691,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -590,6 +710,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -601,7 +727,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="61">
+  <borders count="69">
     <border>
       <left/>
       <right/>
@@ -709,6 +835,64 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -828,6 +1012,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -989,6 +1186,19 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -1041,6 +1251,17 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -1296,6 +1517,15 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1361,7 +1591,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="250">
+  <cellXfs count="279">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1405,28 +1635,31 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1450,33 +1683,35 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1484,32 +1719,35 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1519,444 +1757,471 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2279,7 +2544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.85546875" customWidth="1"/>
@@ -2288,9 +2553,10 @@
     <col min="4" max="4" width="18.42578125" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -2301,10 +2567,11 @@
       <c r="F1" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2313,8 +2580,9 @@
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -2325,42 +2593,45 @@
       <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+        <v>93</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="53" t="s">
-        <v>16</v>
+      <c r="C6" s="58" t="s">
+        <v>17</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -2369,50 +2640,54 @@
       <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="57" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="53" t="s">
-        <v>30</v>
+      <c r="C8" s="58" t="s">
+        <v>31</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="18"/>
       <c r="F8" s="17"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2"/>
-      <c r="C9" s="72" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
+      <c r="C9" s="140" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="140"/>
+      <c r="E9" s="140"/>
       <c r="F9" s="17"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="20" t="s">
         <v>0</v>
@@ -2423,391 +2698,488 @@
       <c r="D10" s="22"/>
       <c r="E10" s="23"/>
       <c r="F10" s="24"/>
-    </row>
-    <row r="11" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="26">
+      <c r="G10" s="25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="27">
         <v>1</v>
       </c>
-      <c r="C11" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="78"/>
-    </row>
-    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28">
+      <c r="C11" s="107" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="108"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="109"/>
+      <c r="G11" s="86" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="28"/>
+      <c r="B12" s="29">
         <v>2</v>
       </c>
-      <c r="C12" s="79" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" s="80"/>
-      <c r="E12" s="80"/>
-      <c r="F12" s="81"/>
-    </row>
-    <row r="13" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="27"/>
-      <c r="B13" s="28">
+      <c r="C12" s="104" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="105"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="106"/>
+      <c r="G12" s="72" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29">
         <v>3</v>
       </c>
-      <c r="C13" s="128"/>
-      <c r="D13" s="129"/>
-      <c r="E13" s="129"/>
-      <c r="F13" s="130"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="29"/>
-      <c r="B14" s="30">
+      <c r="C13" s="126"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="127"/>
+      <c r="F13" s="128"/>
+      <c r="G13" s="72"/>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="30"/>
+      <c r="B14" s="31">
         <v>4</v>
       </c>
-      <c r="C14" s="103"/>
-      <c r="D14" s="104"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="105"/>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A15" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="32">
+      <c r="C14" s="110"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="83"/>
+    </row>
+    <row r="15" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A15" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="33">
         <v>1</v>
       </c>
-      <c r="C15" s="115"/>
-      <c r="D15" s="116"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="117"/>
-    </row>
-    <row r="16" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="27"/>
-      <c r="B16" s="28">
+      <c r="C15" s="113"/>
+      <c r="D15" s="114"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="64"/>
+    </row>
+    <row r="16" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="28"/>
+      <c r="B16" s="29">
         <v>2</v>
       </c>
-      <c r="C16" s="124" t="s">
-        <v>83</v>
-      </c>
-      <c r="D16" s="125"/>
-      <c r="E16" s="126"/>
-      <c r="F16" s="127"/>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="27"/>
-      <c r="B17" s="28">
+      <c r="C16" s="122" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" s="123"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="125"/>
+      <c r="G16" s="72" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="28"/>
+      <c r="B17" s="29">
         <v>3</v>
       </c>
-      <c r="C17" s="124" t="s">
+      <c r="C17" s="122" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="129"/>
+      <c r="E17" s="129"/>
+      <c r="F17" s="130"/>
+      <c r="G17" s="72" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="34"/>
+      <c r="B18" s="31">
+        <v>4</v>
+      </c>
+      <c r="C18" s="104" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="105"/>
+      <c r="E18" s="105"/>
+      <c r="F18" s="106"/>
+      <c r="G18" s="74" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="27">
+        <v>1</v>
+      </c>
+      <c r="C19" s="119" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" s="120"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="85" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="28"/>
+      <c r="B20" s="29">
+        <v>2</v>
+      </c>
+      <c r="C20" s="104" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" s="105"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="106"/>
+      <c r="G20" s="72" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="28"/>
+      <c r="B21" s="29">
+        <v>3</v>
+      </c>
+      <c r="C21" s="104" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" s="105"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="106"/>
+      <c r="G21" s="72" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="71"/>
+      <c r="B22" s="38">
+        <v>4</v>
+      </c>
+      <c r="C22" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="117"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="74" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="33">
+        <v>2</v>
+      </c>
+      <c r="C23" s="107" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="108"/>
+      <c r="E23" s="108"/>
+      <c r="F23" s="109"/>
+      <c r="G23" s="86" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="28"/>
+      <c r="B24" s="29">
+        <v>3</v>
+      </c>
+      <c r="C24" s="104" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="105"/>
+      <c r="E24" s="105"/>
+      <c r="F24" s="106"/>
+      <c r="G24" s="72" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="28"/>
+      <c r="B25" s="29">
+        <v>4</v>
+      </c>
+      <c r="C25" s="144"/>
+      <c r="D25" s="145"/>
+      <c r="E25" s="145"/>
+      <c r="F25" s="146"/>
+      <c r="G25" s="72"/>
+    </row>
+    <row r="26" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="34"/>
+      <c r="B26" s="31">
+        <v>5</v>
+      </c>
+      <c r="C26" s="147"/>
+      <c r="D26" s="148"/>
+      <c r="E26" s="148"/>
+      <c r="F26" s="149"/>
+      <c r="G26" s="73"/>
+    </row>
+    <row r="27" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="33">
+        <v>3</v>
+      </c>
+      <c r="C27" s="150"/>
+      <c r="D27" s="151"/>
+      <c r="E27" s="151"/>
+      <c r="F27" s="152"/>
+      <c r="G27" s="100"/>
+    </row>
+    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="36"/>
+      <c r="B28" s="29">
+        <v>4</v>
+      </c>
+      <c r="C28" s="159" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="131"/>
-      <c r="E17" s="131"/>
-      <c r="F17" s="132"/>
-    </row>
-    <row r="18" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="33"/>
-      <c r="B18" s="30">
+      <c r="D28" s="160"/>
+      <c r="E28" s="160"/>
+      <c r="F28" s="161"/>
+      <c r="G28" s="72" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="37"/>
+      <c r="B29" s="38">
+        <v>5</v>
+      </c>
+      <c r="C29" s="104" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="105"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="106"/>
+      <c r="G29" s="81" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="39"/>
+      <c r="B30" s="31">
+        <v>6</v>
+      </c>
+      <c r="C30" s="156"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="157" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30" s="158"/>
+      <c r="G30" s="74" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A31" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="33">
+        <v>2</v>
+      </c>
+      <c r="C31" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="154"/>
+      <c r="E31" s="154"/>
+      <c r="F31" s="155"/>
+      <c r="G31" s="86" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A32" s="28"/>
+      <c r="B32" s="41">
         <v>4</v>
       </c>
-      <c r="C18" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="80"/>
-      <c r="E18" s="80"/>
-      <c r="F18" s="81"/>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="26">
-        <v>1</v>
-      </c>
-      <c r="C19" s="121" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" s="122"/>
-      <c r="E19" s="122"/>
-      <c r="F19" s="123"/>
-    </row>
-    <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="27"/>
-      <c r="B20" s="28">
-        <v>2</v>
-      </c>
-      <c r="C20" s="79" t="s">
+      <c r="C32" s="141" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" s="142"/>
+      <c r="E32" s="142"/>
+      <c r="F32" s="143"/>
+      <c r="G32" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="81"/>
-    </row>
-    <row r="21" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="27"/>
-      <c r="B21" s="28">
-        <v>3</v>
-      </c>
-      <c r="C21" s="79" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" s="80"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="81"/>
-    </row>
-    <row r="22" spans="1:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="65"/>
-      <c r="B22" s="36">
-        <v>4</v>
-      </c>
-      <c r="C22" s="118" t="s">
-        <v>26</v>
-      </c>
-      <c r="D22" s="119"/>
-      <c r="E22" s="119"/>
-      <c r="F22" s="120"/>
-    </row>
-    <row r="23" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="32">
-        <v>2</v>
-      </c>
-      <c r="C23" s="76" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" s="77"/>
-      <c r="E23" s="77"/>
-      <c r="F23" s="78"/>
-    </row>
-    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="27"/>
-      <c r="B24" s="28">
-        <v>3</v>
-      </c>
-      <c r="C24" s="79" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="80"/>
-      <c r="E24" s="80"/>
-      <c r="F24" s="81"/>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="27"/>
-      <c r="B25" s="28">
-        <v>4</v>
-      </c>
-      <c r="C25" s="82"/>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="84"/>
-    </row>
-    <row r="26" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="33"/>
-      <c r="B26" s="30">
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="42"/>
+      <c r="B33" s="31">
         <v>5</v>
       </c>
-      <c r="C26" s="85"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="87"/>
-    </row>
-    <row r="27" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="32">
-        <v>3</v>
-      </c>
-      <c r="C27" s="88"/>
-      <c r="D27" s="89"/>
-      <c r="E27" s="89"/>
-      <c r="F27" s="90"/>
-    </row>
-    <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="34"/>
-      <c r="B28" s="28">
-        <v>4</v>
-      </c>
-      <c r="C28" s="97" t="s">
+      <c r="C33" s="101" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="102"/>
+      <c r="E33" s="102" t="s">
+        <v>109</v>
+      </c>
+      <c r="F33" s="103"/>
+      <c r="G33" s="74" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="43"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="134"/>
+      <c r="D34" s="135"/>
+      <c r="E34" s="135"/>
+      <c r="F34" s="136"/>
+      <c r="G34" s="45"/>
+    </row>
+    <row r="35" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A35" s="46"/>
+      <c r="B35" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="137" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35" s="138"/>
+      <c r="E35" s="138"/>
+      <c r="F35" s="139"/>
+      <c r="G35" s="79" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A36" s="48"/>
+      <c r="B36" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" s="132"/>
+      <c r="E36" s="132"/>
+      <c r="F36" s="133"/>
+      <c r="G36" s="82" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A37" s="48"/>
+      <c r="B37" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="131" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" s="132"/>
+      <c r="E37" s="132"/>
+      <c r="F37" s="133"/>
+      <c r="G37" s="82" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A38" s="50"/>
+      <c r="B38" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="131" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38" s="132"/>
+      <c r="E38" s="132"/>
+      <c r="F38" s="133"/>
+      <c r="G38" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="D28" s="98"/>
-      <c r="E28" s="98"/>
-      <c r="F28" s="99"/>
-    </row>
-    <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="35"/>
-      <c r="B29" s="36">
-        <v>5</v>
-      </c>
-      <c r="C29" s="79" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" s="80"/>
-      <c r="E29" s="80"/>
-      <c r="F29" s="81"/>
-    </row>
-    <row r="30" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="37"/>
-      <c r="B30" s="30">
-        <v>6</v>
-      </c>
-      <c r="C30" s="94"/>
-      <c r="D30" s="95"/>
-      <c r="E30" s="95" t="s">
-        <v>39</v>
-      </c>
-      <c r="F30" s="96"/>
-    </row>
-    <row r="31" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A31" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" s="32">
-        <v>2</v>
-      </c>
-      <c r="C31" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" s="92"/>
-      <c r="E31" s="92"/>
-      <c r="F31" s="93"/>
-    </row>
-    <row r="32" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A32" s="27"/>
-      <c r="B32" s="39">
-        <v>4</v>
-      </c>
-      <c r="C32" s="73" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" s="74"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="75"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="40"/>
-      <c r="B33" s="30">
-        <v>5</v>
-      </c>
-      <c r="C33" s="112" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="113"/>
-      <c r="E33" s="113" t="s">
-        <v>85</v>
-      </c>
-      <c r="F33" s="114"/>
-    </row>
-    <row r="34" spans="1:6" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="41"/>
-      <c r="B34" s="42"/>
-      <c r="C34" s="106"/>
-      <c r="D34" s="107"/>
-      <c r="E34" s="107"/>
-      <c r="F34" s="108"/>
-    </row>
-    <row r="35" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A35" s="43"/>
-      <c r="B35" s="44" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="109" t="s">
-        <v>36</v>
-      </c>
-      <c r="D35" s="110"/>
-      <c r="E35" s="110"/>
-      <c r="F35" s="111"/>
-    </row>
-    <row r="36" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A36" s="45"/>
-      <c r="B36" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" s="100" t="s">
-        <v>52</v>
-      </c>
-      <c r="D36" s="101"/>
-      <c r="E36" s="101"/>
-      <c r="F36" s="102"/>
-    </row>
-    <row r="37" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A37" s="45"/>
-      <c r="B37" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="C37" s="100" t="s">
-        <v>35</v>
-      </c>
-      <c r="D37" s="101"/>
-      <c r="E37" s="101"/>
-      <c r="F37" s="102"/>
-    </row>
-    <row r="38" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A38" s="47"/>
-      <c r="B38" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="100" t="s">
-        <v>50</v>
-      </c>
-      <c r="D38" s="101"/>
-      <c r="E38" s="101"/>
-      <c r="F38" s="102"/>
-    </row>
-    <row r="39" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="49"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="103"/>
-      <c r="D39" s="104"/>
-      <c r="E39" s="104"/>
-      <c r="F39" s="105"/>
-    </row>
-    <row r="40" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+    </row>
+    <row r="39" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="52"/>
+      <c r="B39" s="31"/>
+      <c r="C39" s="110"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="111"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="53"/>
+    </row>
+    <row r="40" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-    </row>
-    <row r="41" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G40" s="2"/>
+    </row>
+    <row r="41" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A41" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-    </row>
-    <row r="42" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G41" s="2"/>
+    </row>
+    <row r="42" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A42" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-    </row>
-    <row r="43" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G42" s="2"/>
+    </row>
+    <row r="43" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="C21:F21"/>
@@ -2822,25 +3194,6 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="C28:F28"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -2878,7 +3231,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2887,10 +3240,11 @@
     <col min="4" max="4" width="18.5703125" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.42578125" style="2" customWidth="1"/>
     <col min="6" max="6" width="19" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -2898,15 +3252,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -2914,39 +3268,39 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="53" t="s">
-        <v>16</v>
+      <c r="C6" s="58" t="s">
+        <v>17</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -2956,35 +3310,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="57" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="171" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" s="171"/>
-      <c r="E8" s="171"/>
-      <c r="F8" s="171"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>26</v>
+      </c>
+      <c r="C8" s="162" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="162"/>
+      <c r="E8" s="162"/>
+      <c r="F8" s="162"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>0</v>
@@ -2995,344 +3349,385 @@
       <c r="D9" s="22"/>
       <c r="E9" s="23"/>
       <c r="F9" s="24"/>
-    </row>
-    <row r="10" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="26">
+      <c r="G9" s="25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="27">
         <v>1</v>
       </c>
-      <c r="C10" s="178" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" s="179"/>
-      <c r="E10" s="179"/>
-      <c r="F10" s="180"/>
-    </row>
-    <row r="11" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="27"/>
-      <c r="B11" s="28">
+      <c r="C10" s="169" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" s="170"/>
+      <c r="E10" s="170"/>
+      <c r="F10" s="171"/>
+      <c r="G10" s="86" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="28"/>
+      <c r="B11" s="29">
         <v>2</v>
       </c>
-      <c r="C11" s="79" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" s="80"/>
-      <c r="E11" s="80"/>
-      <c r="F11" s="81"/>
-    </row>
-    <row r="12" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="29"/>
-      <c r="B12" s="30">
+      <c r="C11" s="104" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="105"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="106"/>
+      <c r="G11" s="72" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="30"/>
+      <c r="B12" s="31">
         <v>3</v>
       </c>
-      <c r="C12" s="172" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="173"/>
-      <c r="E12" s="173"/>
-      <c r="F12" s="174"/>
-    </row>
-    <row r="13" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="32">
+      <c r="C12" s="163" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="164"/>
+      <c r="E12" s="164"/>
+      <c r="F12" s="165"/>
+      <c r="G12" s="75"/>
+    </row>
+    <row r="13" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="33">
         <v>1</v>
       </c>
-      <c r="C13" s="139" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" s="140"/>
-      <c r="E13" s="141" t="s">
-        <v>90</v>
-      </c>
-      <c r="F13" s="142"/>
-    </row>
-    <row r="14" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28">
+      <c r="C13" s="200" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="201"/>
+      <c r="E13" s="202" t="s">
+        <v>117</v>
+      </c>
+      <c r="F13" s="203"/>
+      <c r="G13" s="86" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="28"/>
+      <c r="B14" s="29">
         <v>2</v>
       </c>
-      <c r="C14" s="175" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" s="176"/>
-      <c r="E14" s="176"/>
-      <c r="F14" s="177"/>
-    </row>
-    <row r="15" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="27"/>
-      <c r="B15" s="28">
+      <c r="C14" s="166" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" s="167"/>
+      <c r="E14" s="167"/>
+      <c r="F14" s="168"/>
+      <c r="G14" s="72" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="28"/>
+      <c r="B15" s="29">
         <v>3</v>
       </c>
-      <c r="C15" s="143" t="s">
-        <v>92</v>
-      </c>
-      <c r="D15" s="144"/>
-      <c r="E15" s="144"/>
-      <c r="F15" s="145"/>
-    </row>
-    <row r="16" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="33"/>
-      <c r="B16" s="30">
+      <c r="C15" s="204" t="s">
+        <v>119</v>
+      </c>
+      <c r="D15" s="205"/>
+      <c r="E15" s="205"/>
+      <c r="F15" s="206"/>
+      <c r="G15" s="72" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="34"/>
+      <c r="B16" s="31">
         <v>4</v>
       </c>
-      <c r="C16" s="133" t="s">
-        <v>105</v>
-      </c>
-      <c r="D16" s="134"/>
-      <c r="E16" s="134"/>
-      <c r="F16" s="135"/>
-    </row>
-    <row r="17" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="32">
+      <c r="C16" s="194" t="s">
+        <v>135</v>
+      </c>
+      <c r="D16" s="195"/>
+      <c r="E16" s="195"/>
+      <c r="F16" s="196"/>
+      <c r="G16" s="74" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="33">
         <v>1</v>
       </c>
-      <c r="C17" s="146" t="s">
+      <c r="C17" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="D17" s="208"/>
+      <c r="E17" s="208" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" s="209"/>
+      <c r="G17" s="86" t="s">
+        <v>49</v>
+      </c>
+      <c r="N17" s="68"/>
+    </row>
+    <row r="18" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="28"/>
+      <c r="B18" s="29">
+        <v>2</v>
+      </c>
+      <c r="C18" s="197" t="s">
+        <v>143</v>
+      </c>
+      <c r="D18" s="198"/>
+      <c r="E18" s="198"/>
+      <c r="F18" s="199"/>
+      <c r="G18" s="72" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="28"/>
+      <c r="B19" s="29">
+        <v>3</v>
+      </c>
+      <c r="C19" s="104" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="105"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="106"/>
+      <c r="G19" s="72" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="34"/>
+      <c r="B20" s="31">
+        <v>4</v>
+      </c>
+      <c r="C20" s="116"/>
+      <c r="D20" s="117"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="118"/>
+      <c r="G20" s="74"/>
+    </row>
+    <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="33">
+        <v>1</v>
+      </c>
+      <c r="C21" s="172"/>
+      <c r="D21" s="173"/>
+      <c r="E21" s="173" t="s">
+        <v>123</v>
+      </c>
+      <c r="F21" s="174"/>
+      <c r="G21" s="86" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="28"/>
+      <c r="B22" s="29">
+        <v>2</v>
+      </c>
+      <c r="C22" s="104" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" s="105"/>
+      <c r="E22" s="105" t="s">
+        <v>120</v>
+      </c>
+      <c r="F22" s="106"/>
+      <c r="G22" s="72" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="34"/>
+      <c r="B23" s="31">
+        <v>3</v>
+      </c>
+      <c r="C23" s="175" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="176"/>
+      <c r="E23" s="176"/>
+      <c r="F23" s="177"/>
+      <c r="G23" s="73"/>
+    </row>
+    <row r="24" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="33">
+        <v>2</v>
+      </c>
+      <c r="C24" s="181" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24" s="182"/>
+      <c r="E24" s="183"/>
+      <c r="F24" s="184"/>
+      <c r="G24" s="99" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="36"/>
+      <c r="B25" s="29">
+        <v>3</v>
+      </c>
+      <c r="C25" s="104" t="s">
+        <v>124</v>
+      </c>
+      <c r="D25" s="105"/>
+      <c r="E25" s="105"/>
+      <c r="F25" s="106"/>
+      <c r="G25" s="72" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="36"/>
+      <c r="B26" s="29">
+        <v>4</v>
+      </c>
+      <c r="C26" s="104" t="s">
+        <v>125</v>
+      </c>
+      <c r="D26" s="105"/>
+      <c r="E26" s="105"/>
+      <c r="F26" s="106"/>
+      <c r="G26" s="72" t="s">
         <v>111</v>
       </c>
-      <c r="D17" s="147"/>
-      <c r="E17" s="147" t="s">
-        <v>112</v>
-      </c>
-      <c r="F17" s="148"/>
-      <c r="M17" s="62"/>
-    </row>
-    <row r="18" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="27"/>
-      <c r="B18" s="28">
+    </row>
+    <row r="27" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="39"/>
+      <c r="B27" s="31">
+        <v>5</v>
+      </c>
+      <c r="C27" s="188"/>
+      <c r="D27" s="189"/>
+      <c r="E27" s="189"/>
+      <c r="F27" s="190"/>
+      <c r="G27" s="73"/>
+    </row>
+    <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="27">
+        <v>1</v>
+      </c>
+      <c r="C28" s="113"/>
+      <c r="D28" s="114"/>
+      <c r="E28" s="114"/>
+      <c r="F28" s="115"/>
+      <c r="G28" s="55"/>
+    </row>
+    <row r="29" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="28"/>
+      <c r="B29" s="41">
         <v>2</v>
       </c>
-      <c r="C18" s="136" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18" s="137"/>
-      <c r="E18" s="137"/>
-      <c r="F18" s="138"/>
-    </row>
-    <row r="19" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="27"/>
-      <c r="B19" s="28">
+      <c r="C29" s="122" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" s="129"/>
+      <c r="E29" s="129"/>
+      <c r="F29" s="130"/>
+      <c r="G29" s="80" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="56"/>
+      <c r="B30" s="38">
         <v>3</v>
       </c>
-      <c r="C19" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="81"/>
-    </row>
-    <row r="20" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="33"/>
-      <c r="B20" s="30">
-        <v>4</v>
-      </c>
-      <c r="C20" s="118"/>
-      <c r="D20" s="119"/>
-      <c r="E20" s="119"/>
-      <c r="F20" s="120"/>
-    </row>
-    <row r="21" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="32">
-        <v>1</v>
-      </c>
-      <c r="C21" s="168"/>
-      <c r="D21" s="169"/>
-      <c r="E21" s="169" t="s">
-        <v>96</v>
-      </c>
-      <c r="F21" s="170"/>
-    </row>
-    <row r="22" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="27"/>
-      <c r="B22" s="28">
-        <v>2</v>
-      </c>
-      <c r="C22" s="79" t="s">
-        <v>95</v>
-      </c>
-      <c r="D22" s="80"/>
-      <c r="E22" s="80" t="s">
-        <v>93</v>
-      </c>
-      <c r="F22" s="81"/>
-    </row>
-    <row r="23" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="33"/>
-      <c r="B23" s="30">
-        <v>3</v>
-      </c>
-      <c r="C23" s="158" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="159"/>
-      <c r="E23" s="159"/>
-      <c r="F23" s="160"/>
-    </row>
-    <row r="24" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="32">
-        <v>2</v>
-      </c>
-      <c r="C24" s="164" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24" s="165"/>
-      <c r="E24" s="166"/>
-      <c r="F24" s="167"/>
-    </row>
-    <row r="25" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="34"/>
-      <c r="B25" s="28">
-        <v>3</v>
-      </c>
-      <c r="C25" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" s="80"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="81"/>
-    </row>
-    <row r="26" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="34"/>
-      <c r="B26" s="28">
-        <v>4</v>
-      </c>
-      <c r="C26" s="79" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" s="80"/>
-      <c r="E26" s="80"/>
-      <c r="F26" s="81"/>
-    </row>
-    <row r="27" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="37"/>
-      <c r="B27" s="30">
-        <v>5</v>
-      </c>
-      <c r="C27" s="152"/>
-      <c r="D27" s="153"/>
-      <c r="E27" s="153"/>
-      <c r="F27" s="154"/>
-    </row>
-    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="26">
-        <v>1</v>
-      </c>
-      <c r="C28" s="115"/>
-      <c r="D28" s="116"/>
-      <c r="E28" s="116"/>
-      <c r="F28" s="117"/>
-    </row>
-    <row r="29" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="27"/>
-      <c r="B29" s="39">
-        <v>2</v>
-      </c>
-      <c r="C29" s="124" t="s">
+      <c r="C30" s="116" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="117"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="118"/>
+      <c r="G30" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="131"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="132"/>
-    </row>
-    <row r="30" spans="1:13" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="51"/>
-      <c r="B30" s="36">
-        <v>3</v>
-      </c>
-      <c r="C30" s="118" t="s">
-        <v>55</v>
-      </c>
-      <c r="D30" s="119"/>
-      <c r="E30" s="119"/>
-      <c r="F30" s="120"/>
-    </row>
-    <row r="31" spans="1:13" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="60"/>
-      <c r="B31" s="61"/>
-      <c r="C31" s="161"/>
-      <c r="D31" s="162"/>
-      <c r="E31" s="162"/>
-      <c r="F31" s="163"/>
-    </row>
-    <row r="32" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="67"/>
-      <c r="B32" s="68" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="155" t="s">
-        <v>86</v>
-      </c>
-      <c r="D32" s="156"/>
-      <c r="E32" s="156"/>
-      <c r="F32" s="157"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="49"/>
-      <c r="B33" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33" s="149" t="s">
-        <v>41</v>
-      </c>
-      <c r="D33" s="150"/>
-      <c r="E33" s="150"/>
-      <c r="F33" s="151"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="31" spans="1:14" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="66"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="178"/>
+      <c r="D31" s="179"/>
+      <c r="E31" s="179"/>
+      <c r="F31" s="180"/>
+      <c r="G31" s="78"/>
+    </row>
+    <row r="32" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="88"/>
+      <c r="B32" s="89" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="191" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" s="192"/>
+      <c r="E32" s="192"/>
+      <c r="F32" s="193"/>
+      <c r="G32" s="90" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="52"/>
+      <c r="B33" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="185" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" s="186"/>
+      <c r="E33" s="186"/>
+      <c r="F33" s="187"/>
+      <c r="G33" s="74" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C32:F32"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C19:F19"/>
@@ -3341,6 +3736,28 @@
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C10:F10"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -3371,7 +3788,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3380,11 +3797,12 @@
     <col min="4" max="4" width="19.42578125" style="2" customWidth="1"/>
     <col min="5" max="5" width="20" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -3392,15 +3810,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -3408,39 +3826,39 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="53" t="s">
-        <v>16</v>
+      <c r="C6" s="58" t="s">
+        <v>17</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -3450,46 +3868,46 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="57" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="181" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="181"/>
-      <c r="E8" s="181"/>
-      <c r="F8" s="181"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>26</v>
+      </c>
+      <c r="C8" s="225" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="225"/>
+      <c r="E8" s="225"/>
+      <c r="F8" s="225"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="202" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" s="202"/>
-      <c r="E9" s="202"/>
-      <c r="F9" s="202"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+      <c r="C9" s="243" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="243"/>
+      <c r="E9" s="243"/>
+      <c r="F9" s="243"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="20" t="s">
         <v>0</v>
@@ -3500,350 +3918,400 @@
       <c r="D10" s="22"/>
       <c r="E10" s="23"/>
       <c r="F10" s="24"/>
-    </row>
-    <row r="11" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="26">
+      <c r="G10" s="25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="27">
         <v>1</v>
       </c>
-      <c r="C11" s="121" t="s">
+      <c r="C11" s="119" t="s">
+        <v>173</v>
+      </c>
+      <c r="D11" s="120"/>
+      <c r="E11" s="120"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="79" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="28"/>
+      <c r="B12" s="29">
+        <v>2</v>
+      </c>
+      <c r="C12" s="104" t="s">
+        <v>174</v>
+      </c>
+      <c r="D12" s="105"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="106"/>
+      <c r="G12" s="80" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29">
+        <v>3</v>
+      </c>
+      <c r="C13" s="222" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" s="223"/>
+      <c r="E13" s="223"/>
+      <c r="F13" s="224"/>
+      <c r="G13" s="72" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="30"/>
+      <c r="B14" s="31">
+        <v>4</v>
+      </c>
+      <c r="C14" s="163" t="s">
+        <v>134</v>
+      </c>
+      <c r="D14" s="164"/>
+      <c r="E14" s="164"/>
+      <c r="F14" s="165"/>
+      <c r="G14" s="74" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="240" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="241"/>
+      <c r="E15" s="241"/>
+      <c r="F15" s="242"/>
+      <c r="G15" s="64"/>
+    </row>
+    <row r="16" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="28"/>
+      <c r="B16" s="27">
+        <v>4</v>
+      </c>
+      <c r="C16" s="104" t="s">
+        <v>172</v>
+      </c>
+      <c r="D16" s="105"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="106"/>
+      <c r="G16" s="80" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="28"/>
+      <c r="B17" s="29">
+        <v>5</v>
+      </c>
+      <c r="C17" s="214" t="s">
+        <v>175</v>
+      </c>
+      <c r="D17" s="215"/>
+      <c r="E17" s="215"/>
+      <c r="F17" s="216"/>
+      <c r="G17" s="84" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="34"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="219"/>
+      <c r="D18" s="220"/>
+      <c r="E18" s="220"/>
+      <c r="F18" s="221"/>
+      <c r="G18" s="73"/>
+    </row>
+    <row r="19" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="33">
+        <v>1</v>
+      </c>
+      <c r="C19" s="207" t="s">
+        <v>144</v>
+      </c>
+      <c r="D19" s="208"/>
+      <c r="E19" s="208"/>
+      <c r="F19" s="209"/>
+      <c r="G19" s="85" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="28"/>
+      <c r="B20" s="29">
+        <v>2</v>
+      </c>
+      <c r="C20" s="122" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="123"/>
+      <c r="E20" s="218" t="s">
+        <v>139</v>
+      </c>
+      <c r="F20" s="130"/>
+      <c r="G20" s="72" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="28"/>
+      <c r="B21" s="29">
+        <v>3</v>
+      </c>
+      <c r="C21" s="122" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" s="123"/>
+      <c r="E21" s="218" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" s="130"/>
+      <c r="G21" s="72" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="34"/>
+      <c r="B22" s="31">
+        <v>4</v>
+      </c>
+      <c r="C22" s="116" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="117"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="72" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="33">
+        <v>1</v>
+      </c>
+      <c r="C23" s="181" t="s">
+        <v>180</v>
+      </c>
+      <c r="D23" s="182"/>
+      <c r="E23" s="182" t="s">
+        <v>137</v>
+      </c>
+      <c r="F23" s="217"/>
+      <c r="G23" s="86" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="28"/>
+      <c r="B24" s="29">
+        <v>2</v>
+      </c>
+      <c r="C24" s="214" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="215"/>
+      <c r="E24" s="215"/>
+      <c r="F24" s="216"/>
+      <c r="G24" s="85" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="28"/>
+      <c r="B25" s="29">
+        <v>3</v>
+      </c>
+      <c r="C25" s="214" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="123"/>
-    </row>
-    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28">
-        <v>2</v>
-      </c>
-      <c r="C12" s="79" t="s">
-        <v>137</v>
-      </c>
-      <c r="D12" s="80"/>
-      <c r="E12" s="80"/>
-      <c r="F12" s="81"/>
-    </row>
-    <row r="13" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="27"/>
-      <c r="B13" s="28">
+      <c r="D25" s="215"/>
+      <c r="E25" s="215"/>
+      <c r="F25" s="216"/>
+      <c r="G25" s="84" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="34"/>
+      <c r="B26" s="31">
+        <v>4</v>
+      </c>
+      <c r="C26" s="237"/>
+      <c r="D26" s="238"/>
+      <c r="E26" s="238"/>
+      <c r="F26" s="239"/>
+      <c r="G26" s="74"/>
+    </row>
+    <row r="27" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="33">
         <v>3</v>
       </c>
-      <c r="C13" s="207" t="s">
-        <v>103</v>
-      </c>
-      <c r="D13" s="208"/>
-      <c r="E13" s="208"/>
-      <c r="F13" s="209"/>
-    </row>
-    <row r="14" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="29"/>
-      <c r="B14" s="30">
-        <v>4</v>
-      </c>
-      <c r="C14" s="172" t="s">
-        <v>104</v>
-      </c>
-      <c r="D14" s="173"/>
-      <c r="E14" s="173"/>
-      <c r="F14" s="174"/>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="199" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="200"/>
-      <c r="E15" s="200"/>
-      <c r="F15" s="201"/>
-    </row>
-    <row r="16" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="27"/>
-      <c r="B16" s="26">
-        <v>4</v>
-      </c>
-      <c r="C16" s="79" t="s">
-        <v>135</v>
-      </c>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="81"/>
-    </row>
-    <row r="17" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="27"/>
-      <c r="B17" s="28">
-        <v>5</v>
-      </c>
-      <c r="C17" s="196" t="s">
-        <v>138</v>
-      </c>
-      <c r="D17" s="197"/>
-      <c r="E17" s="197"/>
-      <c r="F17" s="198"/>
-    </row>
-    <row r="18" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="33"/>
-      <c r="B18" s="30"/>
-      <c r="C18" s="204"/>
-      <c r="D18" s="205"/>
-      <c r="E18" s="205"/>
-      <c r="F18" s="206"/>
-    </row>
-    <row r="19" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="32">
-        <v>1</v>
-      </c>
-      <c r="C19" s="146" t="s">
-        <v>114</v>
-      </c>
-      <c r="D19" s="147"/>
-      <c r="E19" s="147"/>
-      <c r="F19" s="148"/>
-    </row>
-    <row r="20" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="27"/>
-      <c r="B20" s="28">
-        <v>2</v>
-      </c>
-      <c r="C20" s="124" t="s">
-        <v>100</v>
-      </c>
-      <c r="D20" s="125"/>
-      <c r="E20" s="203" t="s">
-        <v>109</v>
-      </c>
-      <c r="F20" s="132"/>
-    </row>
-    <row r="21" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="27"/>
-      <c r="B21" s="28">
-        <v>3</v>
-      </c>
-      <c r="C21" s="124" t="s">
-        <v>110</v>
-      </c>
-      <c r="D21" s="125"/>
-      <c r="E21" s="203" t="s">
-        <v>101</v>
-      </c>
-      <c r="F21" s="132"/>
-    </row>
-    <row r="22" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="33"/>
-      <c r="B22" s="30">
-        <v>4</v>
-      </c>
-      <c r="C22" s="118" t="s">
-        <v>108</v>
-      </c>
-      <c r="D22" s="119"/>
-      <c r="E22" s="119"/>
-      <c r="F22" s="120"/>
-    </row>
-    <row r="23" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="32">
-        <v>1</v>
-      </c>
-      <c r="C23" s="164" t="s">
-        <v>140</v>
-      </c>
-      <c r="D23" s="165"/>
-      <c r="E23" s="165" t="s">
-        <v>107</v>
-      </c>
-      <c r="F23" s="214"/>
-    </row>
-    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="27"/>
-      <c r="B24" s="28">
-        <v>2</v>
-      </c>
-      <c r="C24" s="196" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="197"/>
-      <c r="E24" s="197"/>
-      <c r="F24" s="198"/>
-    </row>
-    <row r="25" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="27"/>
-      <c r="B25" s="28">
-        <v>3</v>
-      </c>
-      <c r="C25" s="196" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" s="197"/>
-      <c r="E25" s="197"/>
-      <c r="F25" s="198"/>
-    </row>
-    <row r="26" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="33"/>
-      <c r="B26" s="30">
-        <v>4</v>
-      </c>
-      <c r="C26" s="193"/>
-      <c r="D26" s="194"/>
-      <c r="E26" s="194"/>
-      <c r="F26" s="195"/>
-    </row>
-    <row r="27" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="32">
-        <v>3</v>
-      </c>
       <c r="C27" s="210" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D27" s="211"/>
       <c r="E27" s="212"/>
       <c r="F27" s="213"/>
-    </row>
-    <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="34"/>
-      <c r="B28" s="26">
+      <c r="G27" s="97" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="36"/>
+      <c r="B28" s="27">
         <v>4</v>
       </c>
-      <c r="C28" s="124" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" s="131"/>
-      <c r="E28" s="131"/>
-      <c r="F28" s="132"/>
-    </row>
-    <row r="29" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="34"/>
-      <c r="B29" s="28">
+      <c r="C28" s="122" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" s="129"/>
+      <c r="E28" s="129"/>
+      <c r="F28" s="130"/>
+      <c r="G28" s="85" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="36"/>
+      <c r="B29" s="29">
         <v>5</v>
       </c>
-      <c r="C29" s="79" t="s">
-        <v>102</v>
-      </c>
-      <c r="D29" s="80"/>
-      <c r="E29" s="80"/>
-      <c r="F29" s="81"/>
-    </row>
-    <row r="30" spans="1:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="37"/>
-      <c r="B30" s="30">
+      <c r="C29" s="104" t="s">
+        <v>132</v>
+      </c>
+      <c r="D29" s="105"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="106"/>
+      <c r="G29" s="85" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="39"/>
+      <c r="B30" s="31">
         <v>6</v>
       </c>
-      <c r="C30" s="183"/>
-      <c r="D30" s="184"/>
-      <c r="E30" s="185" t="s">
-        <v>115</v>
-      </c>
-      <c r="F30" s="186"/>
-    </row>
-    <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" s="32">
+      <c r="C30" s="227"/>
+      <c r="D30" s="228"/>
+      <c r="E30" s="229" t="s">
+        <v>145</v>
+      </c>
+      <c r="F30" s="230"/>
+      <c r="G30" s="74" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="33">
         <v>2</v>
       </c>
-      <c r="C31" s="121" t="s">
-        <v>116</v>
-      </c>
-      <c r="D31" s="122"/>
-      <c r="E31" s="122"/>
-      <c r="F31" s="123"/>
-    </row>
-    <row r="32" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="37"/>
-      <c r="B32" s="70">
+      <c r="C31" s="119" t="s">
+        <v>146</v>
+      </c>
+      <c r="D31" s="120"/>
+      <c r="E31" s="120"/>
+      <c r="F31" s="121"/>
+      <c r="G31" s="86" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="39"/>
+      <c r="B32" s="93">
         <v>3</v>
       </c>
-      <c r="C32" s="118" t="s">
-        <v>116</v>
-      </c>
-      <c r="D32" s="119"/>
-      <c r="E32" s="119"/>
-      <c r="F32" s="120"/>
-    </row>
-    <row r="33" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="71"/>
-      <c r="B33" s="42"/>
-      <c r="C33" s="187"/>
-      <c r="D33" s="188"/>
-      <c r="E33" s="188"/>
-      <c r="F33" s="189"/>
-    </row>
-    <row r="34" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="69"/>
-      <c r="B34" s="59" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="190" t="s">
-        <v>99</v>
-      </c>
-      <c r="D34" s="191"/>
-      <c r="E34" s="191"/>
-      <c r="F34" s="192"/>
-    </row>
-    <row r="35" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="63" t="s">
-        <v>59</v>
-      </c>
-      <c r="B35" s="64"/>
-      <c r="C35" s="182" t="s">
-        <v>60</v>
-      </c>
-      <c r="D35" s="182"/>
-      <c r="E35" s="182"/>
-      <c r="F35" s="182"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C32" s="116" t="s">
+        <v>146</v>
+      </c>
+      <c r="D32" s="117"/>
+      <c r="E32" s="117"/>
+      <c r="F32" s="118"/>
+      <c r="G32" s="98" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="95"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="231"/>
+      <c r="D33" s="232"/>
+      <c r="E33" s="232"/>
+      <c r="F33" s="233"/>
+      <c r="G33" s="96"/>
+    </row>
+    <row r="34" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="92"/>
+      <c r="B34" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="234" t="s">
+        <v>127</v>
+      </c>
+      <c r="D34" s="235"/>
+      <c r="E34" s="235"/>
+      <c r="F34" s="236"/>
+      <c r="G34" s="94" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="B35" s="70"/>
+      <c r="C35" s="226" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="226"/>
+      <c r="E35" s="226"/>
+      <c r="F35" s="226"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="C30:D30"/>
@@ -3860,6 +4328,23 @@
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -3897,7 +4382,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3906,113 +4391,115 @@
     <col min="4" max="4" width="18.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.42578125" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.28515625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8" style="2" customWidth="1"/>
-    <col min="9" max="9" width="20" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="17.85546875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="17.5703125" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="6.85546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" customWidth="1"/>
+    <col min="10" max="10" width="20" style="2" customWidth="1"/>
+    <col min="11" max="11" width="17.140625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="17.85546875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="18.140625" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L2" s="3" t="s">
+      <c r="H2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="H4" s="5"/>
+        <v>93</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>92</v>
+      </c>
       <c r="I4" s="5"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="J4" s="5"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="H5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I5" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="J5" s="9"/>
-      <c r="K5" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="L5" s="11" t="s">
+      <c r="J5" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="K5" s="9"/>
+      <c r="L5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="53" t="s">
-        <v>16</v>
+      <c r="C6" s="58" t="s">
+        <v>17</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -4021,681 +4508,774 @@
       <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="H6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="53" t="s">
+      <c r="J6" s="58" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="13"/>
+      <c r="L6" s="10">
+        <v>4</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="10">
-        <v>4</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="57" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="52" t="s">
+      <c r="H7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="14"/>
-      <c r="K7" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="L7" s="16" t="s">
+      <c r="K7" s="14"/>
+      <c r="L7" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="53" t="s">
-        <v>49</v>
+        <v>26</v>
+      </c>
+      <c r="C8" s="58" t="s">
+        <v>63</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="18"/>
       <c r="F8" s="17"/>
-      <c r="G8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="181" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="181"/>
-      <c r="K8" s="181"/>
-      <c r="L8" s="181"/>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="H8" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="225" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="225"/>
+      <c r="L8" s="225"/>
+      <c r="M8" s="225"/>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
       <c r="F9" s="17"/>
-      <c r="G9" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="202" t="s">
-        <v>80</v>
-      </c>
-      <c r="J9" s="202"/>
-      <c r="K9" s="202"/>
-      <c r="L9" s="202"/>
-    </row>
-    <row r="10" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="H9" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="243" t="s">
+        <v>99</v>
+      </c>
+      <c r="K9" s="243"/>
+      <c r="L9" s="243"/>
+      <c r="M9" s="243"/>
+    </row>
+    <row r="10" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="55"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="20" t="s">
+      <c r="D10" s="60"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="I10" s="21" t="s">
+      <c r="J10" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J10" s="22"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="24"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A11" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="26">
+      <c r="K10" s="22"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A11" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="27">
         <v>1</v>
       </c>
-      <c r="C11" s="215"/>
-      <c r="D11" s="216"/>
-      <c r="E11" s="216"/>
-      <c r="F11" s="217"/>
-      <c r="G11" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="26">
+      <c r="C11" s="254"/>
+      <c r="D11" s="255"/>
+      <c r="E11" s="255"/>
+      <c r="F11" s="256"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="27">
         <v>2</v>
       </c>
-      <c r="I11" s="223" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" s="224"/>
-      <c r="K11" s="224"/>
-      <c r="L11" s="225"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28">
+      <c r="J11" s="257" t="s">
+        <v>29</v>
+      </c>
+      <c r="K11" s="258"/>
+      <c r="L11" s="258"/>
+      <c r="M11" s="259"/>
+      <c r="N11" s="77"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A12" s="28"/>
+      <c r="B12" s="29">
         <v>2</v>
       </c>
-      <c r="C12" s="97" t="s">
-        <v>119</v>
-      </c>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="28">
+      <c r="C12" s="159" t="s">
+        <v>153</v>
+      </c>
+      <c r="D12" s="160"/>
+      <c r="E12" s="160"/>
+      <c r="F12" s="161"/>
+      <c r="G12" s="80" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="28"/>
+      <c r="I12" s="29">
         <v>3</v>
       </c>
-      <c r="I12" s="226"/>
-      <c r="J12" s="227"/>
-      <c r="K12" s="227"/>
-      <c r="L12" s="228"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A13" s="27"/>
-      <c r="B13" s="28">
+      <c r="J12" s="265"/>
+      <c r="K12" s="266"/>
+      <c r="L12" s="266"/>
+      <c r="M12" s="267"/>
+      <c r="N12" s="77"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29">
         <v>3</v>
       </c>
-      <c r="C13" s="175" t="s">
-        <v>120</v>
-      </c>
-      <c r="D13" s="176"/>
-      <c r="E13" s="176"/>
-      <c r="F13" s="177"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="28">
+      <c r="C13" s="166" t="s">
+        <v>154</v>
+      </c>
+      <c r="D13" s="167"/>
+      <c r="E13" s="167"/>
+      <c r="F13" s="168"/>
+      <c r="G13" s="80" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="28"/>
+      <c r="I13" s="29">
         <v>4</v>
       </c>
-      <c r="I13" s="97"/>
-      <c r="J13" s="98"/>
-      <c r="K13" s="98"/>
-      <c r="L13" s="99"/>
-    </row>
-    <row r="14" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="29"/>
-      <c r="B14" s="30">
+      <c r="J13" s="159"/>
+      <c r="K13" s="160"/>
+      <c r="L13" s="160"/>
+      <c r="M13" s="161"/>
+      <c r="N13" s="72"/>
+    </row>
+    <row r="14" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="30"/>
+      <c r="B14" s="31">
         <v>4</v>
       </c>
-      <c r="C14" s="218"/>
-      <c r="D14" s="219"/>
-      <c r="E14" s="219"/>
-      <c r="F14" s="220"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="30">
+      <c r="C14" s="276"/>
+      <c r="D14" s="277"/>
+      <c r="E14" s="277"/>
+      <c r="F14" s="278"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="31">
         <v>5</v>
       </c>
-      <c r="I14" s="246"/>
       <c r="J14" s="247"/>
-      <c r="K14" s="247"/>
+      <c r="K14" s="248"/>
       <c r="L14" s="248"/>
-    </row>
-    <row r="15" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="32">
+      <c r="M14" s="249"/>
+      <c r="N14" s="74"/>
+    </row>
+    <row r="15" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="33">
         <v>2</v>
       </c>
-      <c r="C15" s="215"/>
-      <c r="D15" s="216"/>
-      <c r="E15" s="216"/>
-      <c r="F15" s="217"/>
-      <c r="G15" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="32">
+      <c r="C15" s="254"/>
+      <c r="D15" s="255"/>
+      <c r="E15" s="255"/>
+      <c r="F15" s="256"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="33">
         <v>2</v>
       </c>
-      <c r="I15" s="178" t="s">
-        <v>125</v>
-      </c>
-      <c r="J15" s="179"/>
-      <c r="K15" s="179"/>
-      <c r="L15" s="180"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A16" s="27"/>
-      <c r="B16" s="28">
+      <c r="J15" s="169" t="s">
+        <v>159</v>
+      </c>
+      <c r="K15" s="170"/>
+      <c r="L15" s="170"/>
+      <c r="M15" s="171"/>
+      <c r="N15" s="86" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A16" s="28"/>
+      <c r="B16" s="29">
         <v>3</v>
       </c>
-      <c r="C16" s="124"/>
-      <c r="D16" s="131"/>
-      <c r="E16" s="131"/>
-      <c r="F16" s="132"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="28">
+      <c r="C16" s="122"/>
+      <c r="D16" s="129"/>
+      <c r="E16" s="129"/>
+      <c r="F16" s="130"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="29">
         <v>3</v>
       </c>
-      <c r="I16" s="124" t="s">
-        <v>124</v>
-      </c>
-      <c r="J16" s="131"/>
-      <c r="K16" s="131"/>
-      <c r="L16" s="132"/>
-    </row>
-    <row r="17" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="27"/>
-      <c r="B17" s="28">
+      <c r="J16" s="122" t="s">
+        <v>158</v>
+      </c>
+      <c r="K16" s="129"/>
+      <c r="L16" s="129"/>
+      <c r="M16" s="130"/>
+      <c r="N16" s="80" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="28"/>
+      <c r="B17" s="29">
         <v>4</v>
       </c>
-      <c r="C17" s="79" t="s">
-        <v>122</v>
-      </c>
-      <c r="D17" s="80"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="75"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="28">
+      <c r="C17" s="104" t="s">
+        <v>156</v>
+      </c>
+      <c r="D17" s="105"/>
+      <c r="E17" s="142"/>
+      <c r="F17" s="143"/>
+      <c r="G17" s="72" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17" s="28"/>
+      <c r="I17" s="29">
         <v>4</v>
       </c>
-      <c r="I17" s="124" t="s">
-        <v>139</v>
-      </c>
-      <c r="J17" s="131"/>
-      <c r="K17" s="131"/>
-      <c r="L17" s="132"/>
-    </row>
-    <row r="18" spans="1:12" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="33"/>
-      <c r="B18" s="30">
+      <c r="J17" s="122" t="s">
+        <v>179</v>
+      </c>
+      <c r="K17" s="129"/>
+      <c r="L17" s="129"/>
+      <c r="M17" s="130"/>
+      <c r="N17" s="80" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="34"/>
+      <c r="B18" s="31">
         <v>5</v>
       </c>
-      <c r="C18" s="118"/>
-      <c r="D18" s="221"/>
-      <c r="E18" s="222" t="s">
-        <v>123</v>
-      </c>
-      <c r="F18" s="120"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="30">
+      <c r="C18" s="116"/>
+      <c r="D18" s="274"/>
+      <c r="E18" s="275" t="s">
+        <v>157</v>
+      </c>
+      <c r="F18" s="118"/>
+      <c r="G18" s="72" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" s="34"/>
+      <c r="I18" s="31">
         <v>5</v>
       </c>
-      <c r="I18" s="193"/>
-      <c r="J18" s="194"/>
-      <c r="K18" s="194"/>
-      <c r="L18" s="195"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A19" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="32">
+      <c r="J18" s="237"/>
+      <c r="K18" s="238"/>
+      <c r="L18" s="238"/>
+      <c r="M18" s="239"/>
+      <c r="N18" s="72"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A19" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="33">
         <v>2</v>
       </c>
-      <c r="C19" s="178"/>
-      <c r="D19" s="179"/>
-      <c r="E19" s="179"/>
-      <c r="F19" s="180"/>
-      <c r="G19" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="H19" s="32">
+      <c r="C19" s="169"/>
+      <c r="D19" s="170"/>
+      <c r="E19" s="170"/>
+      <c r="F19" s="171"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="33">
         <v>2</v>
       </c>
-      <c r="I19" s="223" t="s">
-        <v>28</v>
-      </c>
-      <c r="J19" s="224"/>
-      <c r="K19" s="224"/>
-      <c r="L19" s="225"/>
-    </row>
-    <row r="20" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="27"/>
-      <c r="B20" s="28">
+      <c r="J19" s="257" t="s">
+        <v>29</v>
+      </c>
+      <c r="K19" s="258"/>
+      <c r="L19" s="258"/>
+      <c r="M19" s="259"/>
+      <c r="N19" s="35"/>
+    </row>
+    <row r="20" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="28"/>
+      <c r="B20" s="29">
         <v>3</v>
       </c>
-      <c r="C20" s="124" t="s">
-        <v>133</v>
-      </c>
-      <c r="D20" s="131"/>
-      <c r="E20" s="131"/>
-      <c r="F20" s="132"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="28">
+      <c r="C20" s="122" t="s">
+        <v>169</v>
+      </c>
+      <c r="D20" s="129"/>
+      <c r="E20" s="129"/>
+      <c r="F20" s="130"/>
+      <c r="G20" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="28"/>
+      <c r="I20" s="29">
         <v>3</v>
       </c>
-      <c r="I20" s="238"/>
-      <c r="J20" s="239"/>
-      <c r="K20" s="239"/>
-      <c r="L20" s="240"/>
-    </row>
-    <row r="21" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="27"/>
-      <c r="B21" s="28">
+      <c r="J20" s="260"/>
+      <c r="K20" s="261"/>
+      <c r="L20" s="261"/>
+      <c r="M20" s="262"/>
+      <c r="N20" s="77"/>
+    </row>
+    <row r="21" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="28"/>
+      <c r="B21" s="29">
         <v>4</v>
       </c>
-      <c r="C21" s="124" t="s">
-        <v>134</v>
-      </c>
-      <c r="D21" s="131"/>
-      <c r="E21" s="131"/>
-      <c r="F21" s="132"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="28">
+      <c r="C21" s="122" t="s">
+        <v>170</v>
+      </c>
+      <c r="D21" s="129"/>
+      <c r="E21" s="129"/>
+      <c r="F21" s="130"/>
+      <c r="G21" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="28"/>
+      <c r="I21" s="29">
         <v>4</v>
       </c>
-      <c r="I21" s="241"/>
-      <c r="J21" s="242"/>
-      <c r="K21" s="242"/>
-      <c r="L21" s="127"/>
-    </row>
-    <row r="22" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="33"/>
-      <c r="B22" s="30">
+      <c r="J21" s="263"/>
+      <c r="K21" s="264"/>
+      <c r="L21" s="264"/>
+      <c r="M21" s="125"/>
+      <c r="N21" s="80"/>
+    </row>
+    <row r="22" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="34"/>
+      <c r="B22" s="31">
         <v>5</v>
       </c>
-      <c r="C22" s="85"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="87"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="30">
+      <c r="C22" s="147"/>
+      <c r="D22" s="148"/>
+      <c r="E22" s="148"/>
+      <c r="F22" s="149"/>
+      <c r="G22" s="83"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="31">
         <v>5</v>
       </c>
-      <c r="I22" s="243"/>
-      <c r="J22" s="244"/>
-      <c r="K22" s="244"/>
-      <c r="L22" s="245"/>
-    </row>
-    <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="32">
+      <c r="J22" s="251"/>
+      <c r="K22" s="252"/>
+      <c r="L22" s="252"/>
+      <c r="M22" s="253"/>
+      <c r="N22" s="83"/>
+    </row>
+    <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="33">
         <v>2</v>
       </c>
-      <c r="C23" s="88"/>
-      <c r="D23" s="89"/>
-      <c r="E23" s="89"/>
-      <c r="F23" s="90"/>
-      <c r="G23" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="H23" s="32">
+      <c r="C23" s="150"/>
+      <c r="D23" s="151"/>
+      <c r="E23" s="151"/>
+      <c r="F23" s="152"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="I23" s="33">
         <v>5</v>
       </c>
-      <c r="I23" s="88"/>
-      <c r="J23" s="89"/>
-      <c r="K23" s="89"/>
-      <c r="L23" s="90"/>
-    </row>
-    <row r="24" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="27"/>
-      <c r="B24" s="28">
+      <c r="J23" s="150"/>
+      <c r="K23" s="151"/>
+      <c r="L23" s="151"/>
+      <c r="M23" s="152"/>
+      <c r="N23" s="64"/>
+    </row>
+    <row r="24" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="28"/>
+      <c r="B24" s="29">
         <v>3</v>
       </c>
-      <c r="C24" s="124" t="s">
-        <v>117</v>
-      </c>
-      <c r="D24" s="131"/>
-      <c r="E24" s="131"/>
-      <c r="F24" s="132"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="28">
+      <c r="C24" s="122" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="129"/>
+      <c r="E24" s="129"/>
+      <c r="F24" s="130"/>
+      <c r="G24" s="72" t="s">
+        <v>52</v>
+      </c>
+      <c r="H24" s="28"/>
+      <c r="I24" s="29">
         <v>3</v>
       </c>
-      <c r="I24" s="79" t="s">
-        <v>121</v>
-      </c>
-      <c r="J24" s="80"/>
-      <c r="K24" s="80"/>
-      <c r="L24" s="81"/>
-    </row>
-    <row r="25" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="27"/>
-      <c r="B25" s="28">
+      <c r="J24" s="104" t="s">
+        <v>155</v>
+      </c>
+      <c r="K24" s="105"/>
+      <c r="L24" s="105"/>
+      <c r="M24" s="106"/>
+      <c r="N24" s="72" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="28"/>
+      <c r="B25" s="29">
         <v>4</v>
       </c>
-      <c r="C25" s="124" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" s="131"/>
-      <c r="E25" s="131"/>
-      <c r="F25" s="132"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="28">
+      <c r="C25" s="122" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="129"/>
+      <c r="E25" s="129"/>
+      <c r="F25" s="130"/>
+      <c r="G25" s="80" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25" s="28"/>
+      <c r="I25" s="29">
         <v>4</v>
       </c>
-      <c r="I25" s="124" t="s">
-        <v>118</v>
-      </c>
-      <c r="J25" s="131"/>
-      <c r="K25" s="131"/>
-      <c r="L25" s="132"/>
-    </row>
-    <row r="26" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="33"/>
-      <c r="B26" s="30">
+      <c r="J25" s="122" t="s">
+        <v>152</v>
+      </c>
+      <c r="K25" s="129"/>
+      <c r="L25" s="129"/>
+      <c r="M25" s="130"/>
+      <c r="N25" s="72" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="34"/>
+      <c r="B26" s="31">
         <v>5</v>
       </c>
-      <c r="C26" s="118" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="119"/>
-      <c r="E26" s="119"/>
-      <c r="F26" s="120"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="30">
+      <c r="C26" s="116" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="117"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="118"/>
+      <c r="G26" s="72" t="s">
+        <v>52</v>
+      </c>
+      <c r="H26" s="34"/>
+      <c r="I26" s="31">
         <v>5</v>
       </c>
-      <c r="I26" s="243"/>
-      <c r="J26" s="244"/>
-      <c r="K26" s="244"/>
-      <c r="L26" s="245"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A27" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="32">
+      <c r="J26" s="251"/>
+      <c r="K26" s="252"/>
+      <c r="L26" s="252"/>
+      <c r="M26" s="253"/>
+      <c r="N26" s="77"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A27" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="33">
         <v>5</v>
       </c>
-      <c r="C27" s="232"/>
-      <c r="D27" s="233"/>
-      <c r="E27" s="233"/>
-      <c r="F27" s="234"/>
-      <c r="G27" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="32">
+      <c r="C27" s="268"/>
+      <c r="D27" s="269"/>
+      <c r="E27" s="269"/>
+      <c r="F27" s="270"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" s="33">
         <v>5</v>
       </c>
-      <c r="I27" s="215"/>
-      <c r="J27" s="216"/>
-      <c r="K27" s="216"/>
-      <c r="L27" s="217"/>
-    </row>
-    <row r="28" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="34"/>
-      <c r="B28" s="28">
+      <c r="J27" s="254"/>
+      <c r="K27" s="255"/>
+      <c r="L27" s="255"/>
+      <c r="M27" s="256"/>
+      <c r="N27" s="64"/>
+    </row>
+    <row r="28" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="36"/>
+      <c r="B28" s="29">
         <v>6</v>
       </c>
-      <c r="C28" s="82"/>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="84"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="28">
+      <c r="C28" s="144"/>
+      <c r="D28" s="145"/>
+      <c r="E28" s="145"/>
+      <c r="F28" s="146"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="29">
         <v>6</v>
       </c>
-      <c r="I28" s="82"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="83"/>
-      <c r="L28" s="84"/>
-    </row>
-    <row r="29" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="34"/>
-      <c r="B29" s="28">
+      <c r="J28" s="144"/>
+      <c r="K28" s="145"/>
+      <c r="L28" s="145"/>
+      <c r="M28" s="146"/>
+      <c r="N28" s="77"/>
+    </row>
+    <row r="29" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="36"/>
+      <c r="B29" s="29">
         <v>7</v>
       </c>
-      <c r="C29" s="124" t="s">
-        <v>66</v>
-      </c>
-      <c r="D29" s="131"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="132"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="28">
+      <c r="C29" s="122" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" s="129"/>
+      <c r="E29" s="129"/>
+      <c r="F29" s="130"/>
+      <c r="G29" s="72" t="s">
+        <v>149</v>
+      </c>
+      <c r="H29" s="36"/>
+      <c r="I29" s="29">
         <v>7</v>
       </c>
-      <c r="I29" s="124" t="s">
-        <v>131</v>
-      </c>
-      <c r="J29" s="131"/>
-      <c r="K29" s="131"/>
-      <c r="L29" s="132"/>
-    </row>
-    <row r="30" spans="1:12" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="37"/>
-      <c r="B30" s="30">
+      <c r="J29" s="122" t="s">
+        <v>166</v>
+      </c>
+      <c r="K29" s="129"/>
+      <c r="L29" s="129"/>
+      <c r="M29" s="130"/>
+      <c r="N29" s="72" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="39"/>
+      <c r="B30" s="31">
         <v>8</v>
       </c>
-      <c r="C30" s="235" t="s">
-        <v>67</v>
-      </c>
-      <c r="D30" s="236"/>
-      <c r="E30" s="236"/>
-      <c r="F30" s="237"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="30">
+      <c r="C30" s="271" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" s="272"/>
+      <c r="E30" s="272"/>
+      <c r="F30" s="273"/>
+      <c r="G30" s="74" t="s">
+        <v>149</v>
+      </c>
+      <c r="H30" s="39"/>
+      <c r="I30" s="31">
         <v>8</v>
       </c>
-      <c r="I30" s="249" t="s">
-        <v>132</v>
-      </c>
-      <c r="J30" s="185"/>
-      <c r="K30" s="185"/>
-      <c r="L30" s="186"/>
-    </row>
-    <row r="31" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" s="26">
+      <c r="J30" s="250" t="s">
+        <v>167</v>
+      </c>
+      <c r="K30" s="229"/>
+      <c r="L30" s="229"/>
+      <c r="M30" s="230"/>
+      <c r="N30" s="74" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="27">
         <v>1</v>
       </c>
-      <c r="C31" s="164" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31" s="165"/>
-      <c r="E31" s="165"/>
-      <c r="F31" s="214"/>
-      <c r="G31" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="H31" s="26">
+      <c r="C31" s="181" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="182"/>
+      <c r="E31" s="182"/>
+      <c r="F31" s="217"/>
+      <c r="G31" s="85" t="s">
+        <v>84</v>
+      </c>
+      <c r="H31" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="I31" s="27">
         <v>1</v>
       </c>
-      <c r="I31" s="164" t="s">
-        <v>128</v>
-      </c>
-      <c r="J31" s="165"/>
-      <c r="K31" s="165"/>
-      <c r="L31" s="214"/>
-    </row>
-    <row r="32" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="34"/>
-      <c r="B32" s="26">
+      <c r="J31" s="181" t="s">
+        <v>162</v>
+      </c>
+      <c r="K31" s="182"/>
+      <c r="L31" s="182"/>
+      <c r="M31" s="217"/>
+      <c r="N31" s="85" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="36"/>
+      <c r="B32" s="27">
         <v>2</v>
       </c>
-      <c r="C32" s="79" t="s">
-        <v>69</v>
-      </c>
-      <c r="D32" s="80"/>
-      <c r="E32" s="80"/>
-      <c r="F32" s="81"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="26">
+      <c r="C32" s="104" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" s="105"/>
+      <c r="E32" s="105"/>
+      <c r="F32" s="106"/>
+      <c r="G32" s="85" t="s">
+        <v>84</v>
+      </c>
+      <c r="H32" s="36"/>
+      <c r="I32" s="27">
         <v>2</v>
       </c>
-      <c r="I32" s="79" t="s">
-        <v>129</v>
-      </c>
-      <c r="J32" s="80"/>
-      <c r="K32" s="80"/>
-      <c r="L32" s="81"/>
-    </row>
-    <row r="33" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="47"/>
-      <c r="B33" s="28">
+      <c r="J32" s="104" t="s">
+        <v>163</v>
+      </c>
+      <c r="K32" s="105"/>
+      <c r="L32" s="105"/>
+      <c r="M32" s="106"/>
+      <c r="N32" s="85" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="50"/>
+      <c r="B33" s="29">
         <v>3</v>
       </c>
-      <c r="C33" s="79" t="s">
-        <v>126</v>
-      </c>
-      <c r="D33" s="80"/>
-      <c r="E33" s="80" t="s">
-        <v>127</v>
-      </c>
-      <c r="F33" s="81"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="28">
+      <c r="C33" s="104" t="s">
+        <v>160</v>
+      </c>
+      <c r="D33" s="105"/>
+      <c r="E33" s="105" t="s">
+        <v>161</v>
+      </c>
+      <c r="F33" s="106"/>
+      <c r="G33" s="85" t="s">
+        <v>84</v>
+      </c>
+      <c r="H33" s="50"/>
+      <c r="I33" s="29">
         <v>3</v>
       </c>
-      <c r="I33" s="124" t="s">
-        <v>130</v>
-      </c>
-      <c r="J33" s="131"/>
-      <c r="K33" s="131"/>
-      <c r="L33" s="132"/>
-    </row>
-    <row r="34" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="49"/>
-      <c r="B34" s="58"/>
-      <c r="C34" s="229"/>
-      <c r="D34" s="230"/>
-      <c r="E34" s="230"/>
-      <c r="F34" s="231"/>
-      <c r="G34" s="49"/>
-      <c r="H34" s="58">
+      <c r="J33" s="122" t="s">
+        <v>164</v>
+      </c>
+      <c r="K33" s="129"/>
+      <c r="L33" s="129"/>
+      <c r="M33" s="130"/>
+      <c r="N33" s="85" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="52"/>
+      <c r="B34" s="63"/>
+      <c r="C34" s="244"/>
+      <c r="D34" s="245"/>
+      <c r="E34" s="245"/>
+      <c r="F34" s="246"/>
+      <c r="G34" s="73"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="63">
         <v>4</v>
       </c>
-      <c r="I34" s="229"/>
-      <c r="J34" s="230"/>
-      <c r="K34" s="230"/>
-      <c r="L34" s="231"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="J34" s="244"/>
+      <c r="K34" s="245"/>
+      <c r="L34" s="245"/>
+      <c r="M34" s="246"/>
+      <c r="N34" s="73"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35" s="63"/>
-      <c r="H35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" s="69"/>
+      <c r="I35" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K35" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L35" s="66"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="L35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M35" s="76"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H36" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I36" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K36" s="2" t="s">
-        <v>61</v>
+      <c r="L36" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="J12:M12"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C28:F28"/>
@@ -4708,27 +5288,36 @@
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="J18:M18"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6 I6"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5 K5">
+    <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6 J6"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5 L5">
       <formula1>"осенний, весенний"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5 I5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5 J5">
       <formula1>"2025-2026"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4763,14 +5352,14 @@
             <xm:f>IF('\\surgu.ru\all\Users\grn.adm\Desktop\[Пример.xlsx]Лист2'!#REF!=0,"",'\\surgu.ru\all\Users\grn.adm\Desktop\[Пример.xlsx]Лист2'!#REF!)</xm:f>
             <x14:dxf/>
           </x14:cfRule>
-          <xm:sqref>I8</xm:sqref>
+          <xm:sqref>J8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="expression" priority="1" id="{82651CEC-A42C-4DAF-885A-270D42731567}">
             <xm:f>IF('\\surgu.ru\all\Users\grn.adm\Desktop\[Пример.xlsx]Лист2'!#REF!=0,"",'\\surgu.ru\all\Users\grn.adm\Desktop\[Пример.xlsx]Лист2'!#REF!)</xm:f>
             <x14:dxf/>
           </x14:cfRule>
-          <xm:sqref>I9</xm:sqref>
+          <xm:sqref>J9</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
